--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10268,6 +10268,131 @@
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>118080705</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57303</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stenhögarna, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>402521</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6962361</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,7 +10273,7 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,11 +10273,11 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57306</v>
+        <v>57494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,7 +10273,7 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,7 +10273,7 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,7 +10273,7 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 26648-2024 artfynd.xlsx
+++ b/artfynd/A 26648-2024 artfynd.xlsx
@@ -10273,7 +10273,7 @@
         <v>118080705</v>
       </c>
       <c r="B83" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
